--- a/exports/trend_1d/SAIL_full_report.xlsx
+++ b/exports/trend_1d/SAIL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>8.85</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>73.65000000000001</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>72.492343013038</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.03</v>
+        <v>-8.25</v>
       </c>
       <c r="L2" t="n">
-        <v>8.19</v>
+        <v>8.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0.32</v>
+        <v>0.76</v>
       </c>
       <c r="N2" t="n">
-        <v>2.51</v>
+        <v>3.39</v>
       </c>
       <c r="O2" t="n">
         <v>0.65</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.5</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42102</v>
+        <v>42103</v>
       </c>
       <c r="H3" t="n">
-        <v>72.3</v>
+        <v>73.45</v>
       </c>
       <c r="I3" t="n">
         <v>72.99990796071469</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.62</v>
+        <v>-3.23</v>
       </c>
       <c r="L3" t="n">
         <v>8.43</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>11.18</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42130</v>
+        <v>42131</v>
       </c>
       <c r="H4" t="n">
-        <v>70.65000000000001</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>68.85968739508834</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.81</v>
+        <v>-8.58</v>
       </c>
       <c r="L4" t="n">
-        <v>6.06</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>1.17</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.48</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42285</v>
+        <v>42286</v>
       </c>
       <c r="H5" t="n">
-        <v>54.75</v>
+        <v>55.9</v>
       </c>
       <c r="I5" t="n">
         <v>55.81981709814181</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K5" t="n">
-        <v>18.47</v>
+        <v>16.75</v>
       </c>
       <c r="L5" t="n">
         <v>5.29</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>11.72</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42310</v>
+        <v>42311</v>
       </c>
       <c r="H6" t="n">
-        <v>51.55</v>
+        <v>51.05</v>
       </c>
       <c r="I6" t="n">
         <v>51.30026562495593</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.78</v>
+        <v>-8.68</v>
       </c>
       <c r="L6" t="n">
-        <v>8.5</v>
+        <v>9.48</v>
       </c>
       <c r="M6" t="n">
         <v>0.71</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.76</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42356</v>
+        <v>42359</v>
       </c>
       <c r="H7" t="n">
-        <v>47.45</v>
+        <v>48.45</v>
       </c>
       <c r="I7" t="n">
         <v>48.12286746812822</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K7" t="n">
-        <v>7.05</v>
+        <v>5.09</v>
       </c>
       <c r="L7" t="n">
         <v>2.84</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.34</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42381</v>
+        <v>42382</v>
       </c>
       <c r="H8" t="n">
-        <v>45.9</v>
+        <v>45.15</v>
       </c>
       <c r="I8" t="n">
         <v>45.1813718935446</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.26</v>
+        <v>-6.81</v>
       </c>
       <c r="L8" t="n">
-        <v>6.09</v>
+        <v>9.18</v>
       </c>
       <c r="M8" t="n">
         <v>2.2</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.72</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>39.6</v>
+        <v>40.05</v>
       </c>
       <c r="I9" t="n">
         <v>39.75870557797353</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K9" t="n">
-        <v>12.29</v>
+        <v>11.3</v>
       </c>
       <c r="L9" t="n">
         <v>3.65</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.2</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42493</v>
+        <v>42494</v>
       </c>
       <c r="H10" t="n">
-        <v>46.05</v>
+        <v>42.05</v>
       </c>
       <c r="I10" t="n">
         <v>42.56582369148563</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K10" t="n">
-        <v>14.98</v>
+        <v>4.99</v>
       </c>
       <c r="L10" t="n">
         <v>2.12</v>
@@ -1011,7 +1130,7 @@
         <v>1.97</v>
       </c>
       <c r="N10" t="n">
-        <v>6.19</v>
+        <v>8.69</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>18.13</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42529</v>
+        <v>42530</v>
       </c>
       <c r="H11" t="n">
-        <v>42</v>
+        <v>45.1</v>
       </c>
       <c r="I11" t="n">
         <v>43.42392597495632</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>0.12</v>
+        <v>-7.25</v>
       </c>
       <c r="L11" t="n">
         <v>9.390000000000001</v>
@@ -1068,7 +1199,7 @@
         <v>1.53</v>
       </c>
       <c r="N11" t="n">
-        <v>4.91</v>
+        <v>7.38</v>
       </c>
       <c r="O11" t="n">
         <v>-8.69</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.68</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42583</v>
+        <v>42584</v>
       </c>
       <c r="H12" t="n">
-        <v>47.35</v>
+        <v>46.05</v>
       </c>
       <c r="I12" t="n">
         <v>46.17855613682393</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K12" t="n">
-        <v>4.99</v>
+        <v>2.11</v>
       </c>
       <c r="L12" t="n">
         <v>9.76</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>11.96</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42601</v>
+        <v>42604</v>
       </c>
       <c r="H13" t="n">
-        <v>49.55</v>
+        <v>50.2</v>
       </c>
       <c r="I13" t="n">
         <v>50.1273127976002</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.6</v>
+        <v>-9.01</v>
       </c>
       <c r="L13" t="n">
-        <v>8.58</v>
+        <v>10.75</v>
       </c>
       <c r="M13" t="n">
         <v>2.25</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.24</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H14" t="n">
-        <v>50.65</v>
+        <v>47.8</v>
       </c>
       <c r="I14" t="n">
         <v>48.54982826697822</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9</v>
+        <v>-4.78</v>
       </c>
       <c r="L14" t="n">
         <v>5.58</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>14.65</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42670</v>
+        <v>42671</v>
       </c>
       <c r="H15" t="n">
-        <v>49.75</v>
+        <v>52.05</v>
       </c>
       <c r="I15" t="n">
         <v>51.40335150333086</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.08</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>8.68</v>
+        <v>9.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.43</v>
       </c>
       <c r="N15" t="n">
-        <v>4.17</v>
+        <v>4.62</v>
       </c>
       <c r="O15" t="n">
         <v>-5.63</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.07</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42725</v>
+        <v>42726</v>
       </c>
       <c r="H16" t="n">
-        <v>51.25</v>
+        <v>49.75</v>
       </c>
       <c r="I16" t="n">
         <v>49.80593474304642</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.54</v>
+        <v>-4.42</v>
       </c>
       <c r="L16" t="n">
         <v>15.27</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42744</v>
+        <v>42745</v>
       </c>
       <c r="H17" t="n">
-        <v>52.35</v>
+        <v>52.85</v>
       </c>
       <c r="I17" t="n">
         <v>52.79732865877172</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.23</v>
+        <v>-6.23</v>
       </c>
       <c r="L17" t="n">
-        <v>6.33</v>
+        <v>6.83</v>
       </c>
       <c r="M17" t="n">
         <v>1.48</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.97</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42779</v>
+        <v>42780</v>
       </c>
       <c r="H18" t="n">
-        <v>61.65</v>
+        <v>60.75</v>
       </c>
       <c r="I18" t="n">
         <v>61.24055984700605</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K18" t="n">
-        <v>16.65</v>
+        <v>14.95</v>
       </c>
       <c r="L18" t="n">
         <v>0.85</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>12</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42828</v>
+        <v>42830</v>
       </c>
       <c r="H19" t="n">
-        <v>63.1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>65.01512175260885</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.87</v>
+        <v>-7.65</v>
       </c>
       <c r="L19" t="n">
-        <v>6.42</v>
+        <v>8.81</v>
       </c>
       <c r="M19" t="n">
         <v>1.85</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42842</v>
+        <v>42843</v>
       </c>
       <c r="H20" t="n">
-        <v>61.25</v>
+        <v>60.3</v>
       </c>
       <c r="I20" t="n">
         <v>61.15690241778457</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.35</v>
+        <v>-7.8</v>
       </c>
       <c r="L20" t="n">
-        <v>6.73</v>
+        <v>8.1</v>
       </c>
       <c r="M20" t="n">
         <v>0.44</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.32</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42922</v>
+        <v>42923</v>
       </c>
       <c r="H21" t="n">
-        <v>59.65</v>
+        <v>61.65</v>
       </c>
       <c r="I21" t="n">
         <v>60.36329912773187</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K21" t="n">
-        <v>1.08</v>
+        <v>-2.24</v>
       </c>
       <c r="L21" t="n">
         <v>4.89</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.48</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H22" t="n">
-        <v>61.45</v>
+        <v>58.85</v>
       </c>
       <c r="I22" t="n">
         <v>59.51253955047754</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.32</v>
+        <v>-4.54</v>
       </c>
       <c r="L22" t="n">
-        <v>3.57</v>
+        <v>5.19</v>
       </c>
       <c r="M22" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="N22" t="n">
-        <v>3.88</v>
+        <v>4.23</v>
       </c>
       <c r="O22" t="n">
         <v>3.35</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>11.33</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42985</v>
+        <v>42986</v>
       </c>
       <c r="H23" t="n">
-        <v>62.7</v>
+        <v>63.1</v>
       </c>
       <c r="I23" t="n">
         <v>63.00455197695649</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.54</v>
+        <v>-7.22</v>
       </c>
       <c r="L23" t="n">
-        <v>7.39</v>
+        <v>9.52</v>
       </c>
       <c r="M23" t="n">
         <v>1.42</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H24" t="n">
-        <v>61.05</v>
+        <v>57.9</v>
       </c>
       <c r="I24" t="n">
         <v>58.87391641986591</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.25</v>
+        <v>-8.24</v>
       </c>
       <c r="L24" t="n">
-        <v>4.04</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.13</v>
+        <v>5.16</v>
       </c>
       <c r="O24" t="n">
         <v>0.64</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.72</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43024</v>
+        <v>43025</v>
       </c>
       <c r="H25" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="I25" t="n">
         <v>58.41094829191558</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-2.25</v>
       </c>
       <c r="L25" t="n">
         <v>4.23</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H26" t="n">
-        <v>91.84999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>91.28765555933433</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K26" t="n">
-        <v>55.15</v>
+        <v>53.89</v>
       </c>
       <c r="L26" t="n">
         <v>3.13</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>12.54</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43140</v>
+        <v>43143</v>
       </c>
       <c r="H27" t="n">
-        <v>93.95</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="I27" t="n">
         <v>95.0993534000286</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.13</v>
+        <v>-4.67</v>
       </c>
       <c r="L27" t="n">
-        <v>3.68</v>
+        <v>7.9</v>
       </c>
       <c r="M27" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="N27" t="n">
         <v>9.24</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>14.61</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43159</v>
+        <v>43160</v>
       </c>
       <c r="H28" t="n">
-        <v>83.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>81.41647923424122</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>-12.74</v>
+        <v>-15.15</v>
       </c>
       <c r="L28" t="n">
-        <v>14</v>
+        <v>15.42</v>
       </c>
       <c r="M28" t="n">
         <v>1.01</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.32</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43257</v>
+        <v>43258</v>
       </c>
       <c r="H29" t="n">
-        <v>77.3</v>
+        <v>82.8</v>
       </c>
       <c r="I29" t="n">
         <v>78.26085283968094</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K29" t="n">
-        <v>4.45</v>
+        <v>-2.35</v>
       </c>
       <c r="L29" t="n">
         <v>4.88</v>
@@ -2094,7 +2441,7 @@
         <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>4.86</v>
+        <v>7.12</v>
       </c>
       <c r="O29" t="n">
         <v>-2.76</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>15.66</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43291</v>
+        <v>43292</v>
       </c>
       <c r="H30" t="n">
-        <v>81.15000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>78.1836458958433</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.99</v>
+        <v>-6.52</v>
       </c>
       <c r="L30" t="n">
-        <v>6.34</v>
+        <v>6.88</v>
       </c>
       <c r="M30" t="n">
         <v>0.63</v>
       </c>
       <c r="N30" t="n">
-        <v>4.31</v>
+        <v>4.62</v>
       </c>
       <c r="O30" t="n">
         <v>7.12</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43320</v>
+        <v>43321</v>
       </c>
       <c r="H31" t="n">
-        <v>79.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>80.38067746438935</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.45</v>
+        <v>-4.13</v>
       </c>
       <c r="L31" t="n">
         <v>5.94</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>11.73</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H32" t="n">
-        <v>74.2</v>
+        <v>68.25</v>
       </c>
       <c r="I32" t="n">
         <v>73.16903423494125</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K32" t="n">
-        <v>-7.94</v>
+        <v>-15.32</v>
       </c>
       <c r="L32" t="n">
-        <v>12.53</v>
+        <v>15.88</v>
       </c>
       <c r="M32" t="n">
         <v>1.16</v>
       </c>
       <c r="N32" t="n">
-        <v>4.69</v>
+        <v>8.02</v>
       </c>
       <c r="O32" t="n">
         <v>1.64</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>21.07</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H33" t="n">
-        <v>48.25</v>
+        <v>52.35</v>
       </c>
       <c r="I33" t="n">
         <v>50.11297063171117</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K33" t="n">
-        <v>29.3</v>
+        <v>23.3</v>
       </c>
       <c r="L33" t="n">
         <v>9.67</v>
@@ -2322,7 +2717,7 @@
         <v>2.26</v>
       </c>
       <c r="N33" t="n">
-        <v>6.12</v>
+        <v>8.5</v>
       </c>
       <c r="O33" t="n">
         <v>-8.02</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>15.53</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H34" t="n">
-        <v>53</v>
+        <v>52.85</v>
       </c>
       <c r="I34" t="n">
         <v>52.91458676275338</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K34" t="n">
-        <v>1.24</v>
+        <v>0.96</v>
       </c>
       <c r="L34" t="n">
         <v>6.59</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H35" t="n">
-        <v>35.15</v>
+        <v>37</v>
       </c>
       <c r="I35" t="n">
         <v>36.31710423521149</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K35" t="n">
-        <v>33.49</v>
+        <v>29.99</v>
       </c>
       <c r="L35" t="n">
         <v>2.74</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.6</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H36" t="n">
-        <v>46.5</v>
+        <v>44.5</v>
       </c>
       <c r="I36" t="n">
         <v>46.20302523140879</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K36" t="n">
-        <v>25.68</v>
+        <v>20.27</v>
       </c>
       <c r="L36" t="n">
         <v>5.41</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.63</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H37" t="n">
-        <v>26.85</v>
+        <v>28.3</v>
       </c>
       <c r="I37" t="n">
         <v>28.09372707423446</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K37" t="n">
-        <v>39.66</v>
+        <v>36.4</v>
       </c>
       <c r="L37" t="n">
         <v>11.8</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>26.45</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44089</v>
+        <v>44090</v>
       </c>
       <c r="H38" t="n">
-        <v>39.45</v>
+        <v>38</v>
       </c>
       <c r="I38" t="n">
         <v>38.4223647988502</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K38" t="n">
-        <v>39.4</v>
+        <v>34.28</v>
       </c>
       <c r="L38" t="n">
         <v>10.25</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>16.85</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44139</v>
+        <v>44140</v>
       </c>
       <c r="H39" t="n">
-        <v>34.75</v>
+        <v>38.25</v>
       </c>
       <c r="I39" t="n">
         <v>37.45824242418532</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K39" t="n">
-        <v>8.550000000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="L39" t="n">
         <v>4.47</v>
@@ -2664,7 +3131,7 @@
         <v>1.67</v>
       </c>
       <c r="N39" t="n">
-        <v>4.57</v>
+        <v>10.07</v>
       </c>
       <c r="O39" t="n">
         <v>-3.68</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>14.99</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44209</v>
+        <v>44210</v>
       </c>
       <c r="H40" t="n">
-        <v>74.7</v>
+        <v>67.2</v>
       </c>
       <c r="I40" t="n">
         <v>67.60134046286103</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K40" t="n">
-        <v>95.29000000000001</v>
+        <v>75.69</v>
       </c>
       <c r="L40" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>1.21</v>
+        <v>7.63</v>
       </c>
       <c r="N40" t="n">
-        <v>4.32</v>
+        <v>10.04</v>
       </c>
       <c r="O40" t="n">
         <v>10.07</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>20.06</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44249</v>
+        <v>44250</v>
       </c>
       <c r="H41" t="n">
-        <v>66.8</v>
+        <v>70.55</v>
       </c>
       <c r="I41" t="n">
         <v>68.59982381125954</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6</v>
+        <v>-4.99</v>
       </c>
       <c r="L41" t="n">
         <v>7.44</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>17.71</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44335</v>
+        <v>44336</v>
       </c>
       <c r="H42" t="n">
-        <v>128.6</v>
+        <v>121.45</v>
       </c>
       <c r="I42" t="n">
         <v>125.1213964796051</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K42" t="n">
-        <v>82.28</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="L42" t="n">
         <v>5.17</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>21.06</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44405</v>
+        <v>44406</v>
       </c>
       <c r="H43" t="n">
-        <v>133.85</v>
+        <v>141.95</v>
       </c>
       <c r="I43" t="n">
         <v>136.9117516040346</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K43" t="n">
-        <v>-10.21</v>
+        <v>-16.88</v>
       </c>
       <c r="L43" t="n">
-        <v>15.07</v>
+        <v>18.03</v>
       </c>
       <c r="M43" t="n">
         <v>3.48</v>
       </c>
       <c r="N43" t="n">
-        <v>5.08</v>
+        <v>6.05</v>
       </c>
       <c r="O43" t="n">
         <v>-5.56</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>13.19</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H44" t="n">
-        <v>134.1</v>
+        <v>127.25</v>
       </c>
       <c r="I44" t="n">
         <v>127.5388728542202</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.53</v>
+        <v>-10.36</v>
       </c>
       <c r="L44" t="n">
-        <v>6.76</v>
+        <v>12.96</v>
       </c>
       <c r="M44" t="n">
         <v>1.02</v>
       </c>
       <c r="N44" t="n">
-        <v>4.89</v>
+        <v>5.11</v>
       </c>
       <c r="O44" t="n">
         <v>6.05</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>18.17</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44482</v>
+        <v>44483</v>
       </c>
       <c r="H45" t="n">
-        <v>121.75</v>
+        <v>124.2</v>
       </c>
       <c r="I45" t="n">
         <v>122.3844703291591</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K45" t="n">
-        <v>4.32</v>
+        <v>2.4</v>
       </c>
       <c r="L45" t="n">
         <v>8.210000000000001</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.5</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44516</v>
+        <v>44517</v>
       </c>
       <c r="H46" t="n">
-        <v>114.55</v>
+        <v>113.65</v>
       </c>
       <c r="I46" t="n">
         <v>114.3253795252644</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.77</v>
+        <v>-8.49</v>
       </c>
       <c r="L46" t="n">
         <v>9.18</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.52</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44622</v>
+        <v>44623</v>
       </c>
       <c r="H47" t="n">
-        <v>99.34999999999999</v>
+        <v>101.15</v>
       </c>
       <c r="I47" t="n">
         <v>100.6251953226751</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K47" t="n">
-        <v>12.58</v>
+        <v>11</v>
       </c>
       <c r="L47" t="n">
         <v>8.619999999999999</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>13.37</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H48" t="n">
-        <v>101.4</v>
+        <v>96.75</v>
       </c>
       <c r="I48" t="n">
         <v>100.1187327848555</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K48" t="n">
-        <v>0.25</v>
+        <v>-4.35</v>
       </c>
       <c r="L48" t="n">
         <v>7.56</v>
       </c>
       <c r="M48" t="n">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="N48" t="n">
-        <v>4.43</v>
+        <v>4.59</v>
       </c>
       <c r="O48" t="n">
         <v>1.81</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.96</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44764</v>
+        <v>44767</v>
       </c>
       <c r="H49" t="n">
-        <v>75.3</v>
+        <v>76</v>
       </c>
       <c r="I49" t="n">
         <v>75.72027852026454</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K49" t="n">
-        <v>22.17</v>
+        <v>21.45</v>
       </c>
       <c r="L49" t="n">
         <v>3.46</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H50" t="n">
-        <v>80.40000000000001</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="I50" t="n">
         <v>78.25079871222655</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K50" t="n">
-        <v>5.79</v>
+        <v>2.83</v>
       </c>
       <c r="L50" t="n">
         <v>3.22</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>10.09</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H51" t="n">
-        <v>79.59999999999999</v>
+        <v>82.45</v>
       </c>
       <c r="I51" t="n">
         <v>81.21012558897283</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.86</v>
+        <v>-5.5</v>
       </c>
       <c r="L51" t="n">
-        <v>3.77</v>
+        <v>5.82</v>
       </c>
       <c r="M51" t="n">
         <v>2.3</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.7</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H52" t="n">
-        <v>81.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="I52" t="n">
         <v>81.37649193327459</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.27</v>
+        <v>-4.55</v>
       </c>
       <c r="L52" t="n">
         <v>7.52</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>10.56</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H53" t="n">
-        <v>82.65000000000001</v>
+        <v>88.95</v>
       </c>
       <c r="I53" t="n">
         <v>83.20476007400218</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.02</v>
+        <v>-13.02</v>
       </c>
       <c r="L53" t="n">
-        <v>7.31</v>
+        <v>13.72</v>
       </c>
       <c r="M53" t="n">
         <v>1.85</v>
       </c>
       <c r="N53" t="n">
-        <v>5.41</v>
+        <v>7.62</v>
       </c>
       <c r="O53" t="n">
         <v>-3.32</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>13.29</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44963</v>
+        <v>44964</v>
       </c>
       <c r="H54" t="n">
-        <v>84.45</v>
+        <v>82.45</v>
       </c>
       <c r="I54" t="n">
         <v>84.13918202386799</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.06</v>
+        <v>-7.31</v>
       </c>
       <c r="L54" t="n">
-        <v>6.63</v>
+        <v>8.43</v>
       </c>
       <c r="M54" t="n">
         <v>0.79</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.43</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45107</v>
+        <v>45110</v>
       </c>
       <c r="H55" t="n">
-        <v>85.5</v>
+        <v>87.5</v>
       </c>
       <c r="I55" t="n">
         <v>86.27457780652527</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.7</v>
+        <v>-6.12</v>
       </c>
       <c r="L55" t="n">
         <v>8.369999999999999</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>6</v>
+      </c>
+      <c r="U55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.83</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45149</v>
+        <v>45152</v>
       </c>
       <c r="H56" t="n">
-        <v>91.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>90.3443007931575</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K56" t="n">
-        <v>4.11</v>
+        <v>-0.46</v>
       </c>
       <c r="L56" t="n">
         <v>2.17</v>
@@ -3633,7 +4304,7 @@
         <v>1.72</v>
       </c>
       <c r="N56" t="n">
-        <v>2.77</v>
+        <v>4.39</v>
       </c>
       <c r="O56" t="n">
         <v>2.34</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>9.35</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="H57" t="n">
-        <v>88.45</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>90.87777371870476</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.55</v>
+        <v>-4.94</v>
       </c>
       <c r="L57" t="n">
-        <v>4.54</v>
+        <v>5.17</v>
       </c>
       <c r="M57" t="n">
         <v>0.99</v>
       </c>
       <c r="N57" t="n">
-        <v>2.02</v>
+        <v>3.34</v>
       </c>
       <c r="O57" t="n">
         <v>-4.39</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.81</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H58" t="n">
-        <v>92.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="I58" t="n">
         <v>92.81110152332846</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K58" t="n">
-        <v>1.64</v>
+        <v>0.44</v>
       </c>
       <c r="L58" t="n">
         <v>2.84</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>9.65</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45240</v>
+        <v>45242</v>
       </c>
       <c r="H59" t="n">
-        <v>88.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I59" t="n">
         <v>89.34611316088777</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K59" t="n">
-        <v>4.03</v>
+        <v>2.51</v>
       </c>
       <c r="L59" t="n">
         <v>2.94</v>
       </c>
       <c r="M59" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="N59" t="n">
         <v>2.84</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.07</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H60" t="n">
-        <v>114.9</v>
+        <v>108.8</v>
       </c>
       <c r="I60" t="n">
         <v>109.7034324399467</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K60" t="n">
-        <v>28.38</v>
+        <v>21.56</v>
       </c>
       <c r="L60" t="n">
         <v>2.18</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>14.66</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="H61" t="n">
-        <v>119.3</v>
+        <v>128.3</v>
       </c>
       <c r="I61" t="n">
         <v>124.7475241111363</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K61" t="n">
-        <v>-9.65</v>
+        <v>-17.92</v>
       </c>
       <c r="L61" t="n">
-        <v>14.75</v>
+        <v>19.16</v>
       </c>
       <c r="M61" t="n">
         <v>1.18</v>
       </c>
       <c r="N61" t="n">
-        <v>5.74</v>
+        <v>7.54</v>
       </c>
       <c r="O61" t="n">
         <v>-5.31</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>14.82</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H62" t="n">
-        <v>133.65</v>
+        <v>122.75</v>
       </c>
       <c r="I62" t="n">
         <v>126.9277454574969</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K62" t="n">
-        <v>4.17</v>
+        <v>-4.33</v>
       </c>
       <c r="L62" t="n">
         <v>6.63</v>
@@ -3975,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.88</v>
+        <v>8.16</v>
       </c>
       <c r="O62" t="n">
         <v>7.54</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>23.67</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45353</v>
+        <v>45355</v>
       </c>
       <c r="H63" t="n">
-        <v>137.65</v>
+        <v>141.65</v>
       </c>
       <c r="I63" t="n">
         <v>138.4741764908537</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>-12.14</v>
+        <v>-15.4</v>
       </c>
       <c r="L63" t="n">
-        <v>12.83</v>
+        <v>18.13</v>
       </c>
       <c r="M63" t="n">
         <v>1.49</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>16.37</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H64" t="n">
-        <v>129.75</v>
+        <v>118.7</v>
       </c>
       <c r="I64" t="n">
         <v>121.0447203043509</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K64" t="n">
-        <v>-8.4</v>
+        <v>-16.2</v>
       </c>
       <c r="L64" t="n">
-        <v>9.279999999999999</v>
+        <v>17.15</v>
       </c>
       <c r="M64" t="n">
         <v>0.32</v>
       </c>
       <c r="N64" t="n">
-        <v>3.39</v>
+        <v>8.52</v>
       </c>
       <c r="O64" t="n">
         <v>2.91</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>22.83</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H65" t="n">
-        <v>140.75</v>
+        <v>147.85</v>
       </c>
       <c r="I65" t="n">
         <v>142.2311520967355</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K65" t="n">
-        <v>-18.58</v>
+        <v>-24.56</v>
       </c>
       <c r="L65" t="n">
-        <v>18.96</v>
+        <v>26.92</v>
       </c>
       <c r="M65" t="n">
         <v>2.99</v>
       </c>
       <c r="N65" t="n">
-        <v>4.84</v>
+        <v>5.04</v>
       </c>
       <c r="O65" t="n">
         <v>-8.52</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>15.1</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H66" t="n">
-        <v>166.35</v>
+        <v>133.05</v>
       </c>
       <c r="I66" t="n">
         <v>150.6206109678426</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K66" t="n">
-        <v>12.51</v>
+        <v>-10.01</v>
       </c>
       <c r="L66" t="n">
-        <v>5.61</v>
+        <v>15.59</v>
       </c>
       <c r="M66" t="n">
         <v>1.58</v>
       </c>
       <c r="N66" t="n">
-        <v>4.55</v>
+        <v>20.02</v>
       </c>
       <c r="O66" t="n">
         <v>5.04</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>31.28</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="H67" t="n">
-        <v>134.23</v>
+        <v>139.2</v>
       </c>
       <c r="I67" t="n">
         <v>137.8408372519779</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.89</v>
+        <v>-4.62</v>
       </c>
       <c r="L67" t="n">
         <v>23.94</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>11.25</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45581</v>
+        <v>45582</v>
       </c>
       <c r="H68" t="n">
-        <v>129.92</v>
+        <v>127.83</v>
       </c>
       <c r="I68" t="n">
         <v>129.6704989199716</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K68" t="n">
-        <v>-6.67</v>
+        <v>-8.17</v>
       </c>
       <c r="L68" t="n">
-        <v>8.16</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M68" t="n">
         <v>1.76</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>11.37</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H69" t="n">
-        <v>122.47</v>
+        <v>123.89</v>
       </c>
       <c r="I69" t="n">
         <v>123.25999860309</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K69" t="n">
-        <v>4.19</v>
+        <v>3.08</v>
       </c>
       <c r="L69" t="n">
         <v>2.63</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>8.27</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H70" t="n">
-        <v>118.91</v>
+        <v>116.1</v>
       </c>
       <c r="I70" t="n">
         <v>117.7616924163799</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.02</v>
+        <v>-6.29</v>
       </c>
       <c r="L70" t="n">
-        <v>5.96</v>
+        <v>7.01</v>
       </c>
       <c r="M70" t="n">
         <v>2.24</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,25 +5318,25 @@
         <v>11.66</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H71" t="n">
-        <v>108.91</v>
+        <v>113.23</v>
       </c>
       <c r="I71" t="n">
         <v>113.1582342147506</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K71" t="n">
-        <v>6.19</v>
+        <v>2.47</v>
       </c>
       <c r="L71" t="n">
         <v>4.75</v>
       </c>
       <c r="M71" t="n">
-        <v>1.69</v>
+        <v>4.21</v>
       </c>
       <c r="N71" t="n">
         <v>5.78</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>11.9</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H72" t="n">
-        <v>112.6</v>
+        <v>104.63</v>
       </c>
       <c r="I72" t="n">
         <v>107.2969395898725</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-7.6</v>
       </c>
       <c r="L72" t="n">
-        <v>2.31</v>
+        <v>10.5</v>
       </c>
       <c r="M72" t="n">
-        <v>1.18</v>
+        <v>10</v>
       </c>
       <c r="N72" t="n">
-        <v>5.01</v>
+        <v>7.08</v>
       </c>
       <c r="O72" t="n">
         <v>3.97</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>12.53</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="H73" t="n">
-        <v>116.76</v>
+        <v>118.03</v>
       </c>
       <c r="I73" t="n">
         <v>117.3420524350847</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K73" t="n">
-        <v>-11.59</v>
+        <v>-12.81</v>
       </c>
       <c r="L73" t="n">
         <v>13.72</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>10.99</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H74" t="n">
-        <v>127.03</v>
+        <v>125.15</v>
       </c>
       <c r="I74" t="n">
         <v>125.52373483505</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K74" t="n">
-        <v>7.63</v>
+        <v>6.03</v>
       </c>
       <c r="L74" t="n">
         <v>9.98</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>7.59</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="H75" t="n">
-        <v>133.34</v>
+        <v>137.48</v>
       </c>
       <c r="I75" t="n">
         <v>134.6538531087262</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.54</v>
+        <v>-9.85</v>
       </c>
       <c r="L75" t="n">
-        <v>8.94</v>
+        <v>10.27</v>
       </c>
       <c r="M75" t="n">
         <v>1.15</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,25 +5663,25 @@
         <v>9.33</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H76" t="n">
-        <v>130.67</v>
+        <v>125.59</v>
       </c>
       <c r="I76" t="n">
         <v>128.3488540862941</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.95</v>
+        <v>-8.65</v>
       </c>
       <c r="L76" t="n">
-        <v>5.38</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M76" t="n">
-        <v>0.76</v>
+        <v>1.58</v>
       </c>
       <c r="N76" t="n">
         <v>4.04</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>9.15</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="H77" t="n">
-        <v>123.09</v>
+        <v>129.68</v>
       </c>
       <c r="I77" t="n">
         <v>127.4624833236372</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K77" t="n">
-        <v>1.99</v>
+        <v>-3.26</v>
       </c>
       <c r="L77" t="n">
-        <v>2.4</v>
+        <v>3.51</v>
       </c>
       <c r="M77" t="n">
         <v>2.02</v>
       </c>
       <c r="N77" t="n">
-        <v>4.46</v>
+        <v>5.35</v>
       </c>
       <c r="O77" t="n">
         <v>-3.89</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>9.82</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H78" t="n">
-        <v>134.08</v>
+        <v>132.08</v>
       </c>
       <c r="I78" t="n">
         <v>132.1913320127091</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K78" t="n">
-        <v>3.39</v>
+        <v>1.85</v>
       </c>
       <c r="L78" t="n">
         <v>4.72</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>9.49</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="H79" t="n">
-        <v>134.09</v>
+        <v>141.02</v>
       </c>
       <c r="I79" t="n">
         <v>135.2790993287667</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.52</v>
+        <v>-6.77</v>
       </c>
       <c r="L79" t="n">
-        <v>5.73</v>
+        <v>7.36</v>
       </c>
       <c r="M79" t="n">
         <v>1.21</v>
       </c>
       <c r="N79" t="n">
-        <v>3.53</v>
+        <v>5.17</v>
       </c>
       <c r="O79" t="n">
         <v>-1.49</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>11.05</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H80" t="n">
-        <v>154.94</v>
+        <v>149.52</v>
       </c>
       <c r="I80" t="n">
         <v>150.0449621788835</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K80" t="n">
-        <v>9.869999999999999</v>
+        <v>6.03</v>
       </c>
       <c r="L80" t="n">
         <v>5.3</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>12.18</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H81" t="n">
-        <v>163.35</v>
+        <v>166.02</v>
       </c>
       <c r="I81" t="n">
         <v>165.7788981266901</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K81" t="n">
-        <v>-9.25</v>
+        <v>-11.04</v>
       </c>
       <c r="L81" t="n">
         <v>13.03</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>12.93</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H82" t="n">
-        <v>190.56</v>
+        <v>183.78</v>
       </c>
       <c r="I82" t="n">
         <v>185.9464112822487</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K82" t="n">
-        <v>14.78</v>
+        <v>10.7</v>
       </c>
       <c r="L82" t="n">
         <v>3.17</v>
@@ -5115,7 +6098,7 @@
         <v>1.95</v>
       </c>
       <c r="N82" t="n">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="O82" t="n">
         <v>1.63</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>12.25</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="H83" t="n">
-        <v>173.55</v>
+        <v>175.5</v>
       </c>
       <c r="I83" t="n">
         <v>173.6058586729766</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K83" t="n">
-        <v>5.57</v>
+        <v>4.51</v>
       </c>
       <c r="L83" t="n">
         <v>2.27</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>10.49</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H84" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I84" t="n">
         <v>176.9574363895127</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K84" t="n">
-        <v>1.99</v>
+        <v>-1.42</v>
       </c>
       <c r="L84" t="n">
         <v>9.56</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,14 @@
       <c r="Q85" t="n">
         <v>30</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10247,7 +11274,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="6">
@@ -10257,7 +11284,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -10267,7 +11294,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8">
@@ -10277,7 +11304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -10287,7 +11314,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="10">
@@ -10297,7 +11324,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -10337,7 +11364,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.05</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -10347,7 +11374,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.88</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="16">
@@ -10357,7 +11384,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.16</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="17">
@@ -10367,7 +11394,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95.29000000000001</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="18">
@@ -10377,7 +11404,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.4</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="19">
@@ -10387,7 +11414,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.06</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="20">
@@ -10397,7 +11424,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.34</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="21">
@@ -10407,7 +11434,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.94</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="22">
@@ -10417,7 +11444,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -10427,7 +11454,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -10437,7 +11464,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="25">
@@ -10447,7 +11474,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -10457,7 +11484,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.24</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="27">
@@ -10467,7 +11494,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.64</v>
+        <v>20.02</v>
       </c>
     </row>
     <row r="28">
@@ -10477,7 +11504,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
